--- a/Jaguars-Jumps-Roster.xlsx
+++ b/Jaguars-Jumps-Roster.xlsx
@@ -397,11 +397,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D16"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -414,6 +415,9 @@
       <c r="C1" t="str">
         <v>Role</v>
       </c>
+      <c r="D1" t="str">
+        <v>Gender</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -425,6 +429,9 @@
       <c r="C2" t="str">
         <v>admin</v>
       </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -436,6 +443,9 @@
       <c r="C3" t="str">
         <v/>
       </c>
+      <c r="D3" t="str">
+        <v>Boys</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -447,6 +457,9 @@
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="D4" t="str">
+        <v>Boys</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -458,6 +471,9 @@
       <c r="C5" t="str">
         <v/>
       </c>
+      <c r="D5" t="str">
+        <v>Boys</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -469,6 +485,9 @@
       <c r="C6" t="str">
         <v/>
       </c>
+      <c r="D6" t="str">
+        <v>Boys</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -480,6 +499,9 @@
       <c r="C7" t="str">
         <v/>
       </c>
+      <c r="D7" t="str">
+        <v>Boys</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -491,6 +513,9 @@
       <c r="C8" t="str">
         <v/>
       </c>
+      <c r="D8" t="str">
+        <v>Boys</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -502,6 +527,9 @@
       <c r="C9" t="str">
         <v/>
       </c>
+      <c r="D9" t="str">
+        <v>Boys</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -513,6 +541,9 @@
       <c r="C10" t="str">
         <v/>
       </c>
+      <c r="D10" t="str">
+        <v>Boys</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -524,6 +555,9 @@
       <c r="C11" t="str">
         <v/>
       </c>
+      <c r="D11" t="str">
+        <v>Girls</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -535,6 +569,9 @@
       <c r="C12" t="str">
         <v/>
       </c>
+      <c r="D12" t="str">
+        <v>Girls</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -546,6 +583,9 @@
       <c r="C13" t="str">
         <v/>
       </c>
+      <c r="D13" t="str">
+        <v>Girls</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -557,6 +597,9 @@
       <c r="C14" t="str">
         <v/>
       </c>
+      <c r="D14" t="str">
+        <v>Girls</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -568,6 +611,9 @@
       <c r="C15" t="str">
         <v/>
       </c>
+      <c r="D15" t="str">
+        <v>Girls</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -579,10 +625,13 @@
       <c r="C16" t="str">
         <v/>
       </c>
+      <c r="D16" t="str">
+        <v>Girls</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
   </ignoredErrors>
 </worksheet>
 </file>